--- a/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,3; 47,54</t>
+          <t>38,5; 47,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,37; 55,6</t>
+          <t>45,0; 54,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,2; 49,82</t>
+          <t>39,31; 49,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,64; 35,96</t>
+          <t>27,8; 35,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,34; 54,78</t>
+          <t>42,88; 54,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,99; 56,86</t>
+          <t>45,22; 56,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,99; 55,97</t>
+          <t>45,07; 56,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,17; 37,82</t>
+          <t>30,24; 38,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,59; 48,93</t>
+          <t>41,61; 48,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,94; 53,88</t>
+          <t>46,29; 53,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,44; 51,19</t>
+          <t>43,84; 51,26</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,83; 35,45</t>
+          <t>29,81; 36,01</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,57; 49,11</t>
+          <t>38,99; 49,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,09; 56,79</t>
+          <t>46,65; 57,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,29; 52,29</t>
+          <t>41,69; 52,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,86; 37,09</t>
+          <t>28,21; 37,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>46,81; 57,03</t>
+          <t>47,14; 57,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,76; 67,25</t>
+          <t>54,94; 66,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,28; 54,66</t>
+          <t>44,48; 54,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,38; 34,46</t>
+          <t>26,06; 33,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,82; 52,12</t>
+          <t>44,54; 52,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51,94; 59,89</t>
+          <t>52,48; 59,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,6; 51,91</t>
+          <t>44,88; 52,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,55; 34,32</t>
+          <t>28,46; 34,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,95; 49,29</t>
+          <t>41,05; 49,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,71; 61,08</t>
+          <t>53,21; 61,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,77; 59,78</t>
+          <t>50,69; 59,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 33,09</t>
+          <t>8,3; 33,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,4; 63,01</t>
+          <t>48,11; 63,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,18; 75,62</t>
+          <t>63,73; 75,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,65; 73,03</t>
+          <t>59,03; 73,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,46; 50,79</t>
+          <t>38,4; 50,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,59; 51,21</t>
+          <t>43,87; 51,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57,65; 64,15</t>
+          <t>57,55; 64,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>54,15; 61,72</t>
+          <t>53,88; 61,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 36,51</t>
+          <t>11,83; 36,27</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,8; 51,41</t>
+          <t>45,42; 51,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,16; 59,85</t>
+          <t>53,95; 60,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50,1; 56,04</t>
+          <t>49,94; 56,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,99; 40,14</t>
+          <t>33,87; 40,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,97; 62,87</t>
+          <t>55,81; 63,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,5; 66,42</t>
+          <t>59,22; 66,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,12; 57,0</t>
+          <t>50,19; 57,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,01; 73,66</t>
+          <t>36,03; 71,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,43; 54,82</t>
+          <t>50,21; 54,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,84; 61,6</t>
+          <t>57,12; 61,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,72; 55,12</t>
+          <t>50,82; 55,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,26; 59,14</t>
+          <t>36,49; 62,19</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,47; 53,87</t>
+          <t>43,36; 53,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,12; 60,85</t>
+          <t>52,23; 60,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49,07; 57,5</t>
+          <t>48,49; 56,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,74; 43,1</t>
+          <t>33,26; 43,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,62; 65,17</t>
+          <t>56,01; 64,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,13; 76,5</t>
+          <t>70,03; 76,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,52; 73,36</t>
+          <t>66,57; 73,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,67; 48,75</t>
+          <t>32,64; 49,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,69; 59,58</t>
+          <t>52,64; 59,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,56; 69,29</t>
+          <t>64,08; 69,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,37; 64,62</t>
+          <t>59,46; 64,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,21; 45,03</t>
+          <t>34,03; 44,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,65; 28,24</t>
+          <t>19,2; 28,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,28; 42,82</t>
+          <t>31,56; 43,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27,22; 37,59</t>
+          <t>26,75; 37,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16,28; 35,53</t>
+          <t>17,14; 36,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>64,0; 69,37</t>
+          <t>63,75; 69,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,62; 75,04</t>
+          <t>70,24; 75,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,56; 70,19</t>
+          <t>64,78; 70,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,33; 47,98</t>
+          <t>41,1; 47,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55,9; 60,79</t>
+          <t>55,8; 60,65</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63,07; 68,57</t>
+          <t>62,89; 68,35</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,46; 62,89</t>
+          <t>57,67; 62,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,74; 43,41</t>
+          <t>36,63; 43,64</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,59; 46,1</t>
+          <t>42,63; 46,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,12; 55,58</t>
+          <t>52,24; 55,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,03; 51,65</t>
+          <t>48,25; 51,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,1; 34,7</t>
+          <t>25,48; 34,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,75; 62,06</t>
+          <t>58,79; 62,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,02; 69,19</t>
+          <t>65,93; 69,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,45; 62,85</t>
+          <t>59,53; 62,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,5; 54,15</t>
+          <t>38,74; 53,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,35; 53,82</t>
+          <t>51,2; 53,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,63; 62,04</t>
+          <t>59,71; 61,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54,44; 56,74</t>
+          <t>54,46; 56,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,61; 42,54</t>
+          <t>33,74; 43,28</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>181469; 225223</t>
+          <t>182396; 226687</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>198343; 243067</t>
+          <t>196732; 239453</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>172507; 213778</t>
+          <t>168658; 213035</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139637; 181676</t>
+          <t>140431; 180816</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>132904; 167995</t>
+          <t>131496; 165635</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>141477; 178811</t>
+          <t>142194; 179107</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>156123; 194241</t>
+          <t>156429; 194818</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>135005; 169253</t>
+          <t>135309; 170259</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>324616; 381890</t>
+          <t>324745; 378626</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>345338; 404987</t>
+          <t>347918; 404971</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337189; 397325</t>
+          <t>340243; 397856</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>284231; 337721</t>
+          <t>284018; 343020</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>141535; 180208</t>
+          <t>143069; 182993</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>193008; 237826</t>
+          <t>195382; 239947</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159547; 197263</t>
+          <t>157263; 197306</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125991; 167738</t>
+          <t>127576; 167613</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>174059; 212067</t>
+          <t>175313; 213819</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>188475; 227310</t>
+          <t>185696; 223689</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>164837; 203468</t>
+          <t>165573; 204473</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100915; 131855</t>
+          <t>99695; 129634</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>331155; 385034</t>
+          <t>329030; 385211</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>393049; 453238</t>
+          <t>397150; 453735</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>334240; 389041</t>
+          <t>336404; 390186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>238303; 286479</t>
+          <t>237604; 285335</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>222115; 267332</t>
+          <t>222670; 268598</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>331769; 384467</t>
+          <t>334909; 384891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264971; 311986</t>
+          <t>264580; 309409</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49268; 221146</t>
+          <t>55457; 221450</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>81209; 105727</t>
+          <t>80721; 106450</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>166958; 196714</t>
+          <t>165781; 195956</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97436; 121321</t>
+          <t>98064; 122223</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64191; 84769</t>
+          <t>64089; 84586</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>309554; 363652</t>
+          <t>311526; 366582</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>512785; 570607</t>
+          <t>511954; 573947</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>372573; 424687</t>
+          <t>370694; 425675</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85650; 304912</t>
+          <t>98770; 302907</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>567162; 636615</t>
+          <t>562503; 637395</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>627763; 693648</t>
+          <t>625322; 695489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>575913; 644257</t>
+          <t>574088; 645111</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>351732; 415413</t>
+          <t>350482; 417016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>399778; 449048</t>
+          <t>398660; 456651</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>456156; 509197</t>
+          <t>454000; 509879</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>413921; 470767</t>
+          <t>414547; 471667</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>352189; 720499</t>
+          <t>352381; 694981</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>984684; 1070372</t>
+          <t>980415; 1065684</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094476; 1186204</t>
+          <t>1100000; 1190245</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1001904; 1088969</t>
+          <t>1003980; 1094351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>729884; 1190427</t>
+          <t>734480; 1251852</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>152393; 188841</t>
+          <t>151986; 188196</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>266143; 310683</t>
+          <t>266682; 311180</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>304601; 356920</t>
+          <t>300960; 352077</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>160265; 204746</t>
+          <t>158013; 205252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>322022; 370681</t>
+          <t>318572; 369317</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>534032; 582598</t>
+          <t>533315; 583779</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>491061; 541574</t>
+          <t>491479; 541963</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>258050; 410131</t>
+          <t>274571; 414189</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484355; 547731</t>
+          <t>483920; 545736</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>808507; 881479</t>
+          <t>815116; 881465</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>806783; 878148</t>
+          <t>808005; 879650</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>450348; 592780</t>
+          <t>447951; 592251</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55616; 84212</t>
+          <t>57264; 85926</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>83484; 114288</t>
+          <t>84236; 117094</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78172; 107939</t>
+          <t>76807; 106710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39163; 85456</t>
+          <t>41217; 88121</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>799203; 866260</t>
+          <t>796023; 862353</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>772321; 832446</t>
+          <t>779183; 834430</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>698596; 759480</t>
+          <t>700978; 763766</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>314682; 365301</t>
+          <t>312937; 363816</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>864787; 940346</t>
+          <t>863143; 938164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>868056; 943634</t>
+          <t>865567; 940630</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>786739; 861122</t>
+          <t>789649; 861606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>368131; 434962</t>
+          <t>367038; 437228</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1392784; 1507647</t>
+          <t>1394034; 1509515</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1783544; 1901746</t>
+          <t>1787502; 1904759</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1626259; 1748671</t>
+          <t>1633597; 1748961</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>847260; 1171380</t>
+          <t>860155; 1171427</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1984792; 2096394</t>
+          <t>1986096; 2097837</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2343648; 2456436</t>
+          <t>2340512; 2456362</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2099360; 2219657</t>
+          <t>2102521; 2221717</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1377497; 1937183</t>
+          <t>1386144; 1907649</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3414032; 3578311</t>
+          <t>3404040; 3568526</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4157191; 4325228</t>
+          <t>4163000; 4313943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3765985; 3924873</t>
+          <t>3767104; 3930077</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2337048; 2958346</t>
+          <t>2346399; 3009835</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,5; 47,85</t>
+          <t>37,94; 47,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>45,0; 54,77</t>
+          <t>45,14; 54,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,31; 49,65</t>
+          <t>39,48; 49,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,8; 35,79</t>
+          <t>27,56; 35,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,88; 54,01</t>
+          <t>42,76; 54,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,22; 56,96</t>
+          <t>44,46; 56,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,07; 56,13</t>
+          <t>44,71; 56,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,24; 38,05</t>
+          <t>30,48; 38,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41,61; 48,51</t>
+          <t>40,99; 48,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,29; 53,88</t>
+          <t>46,33; 54,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,84; 51,26</t>
+          <t>43,47; 50,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,81; 36,01</t>
+          <t>30,04; 35,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,99; 49,87</t>
+          <t>38,87; 49,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,65; 57,29</t>
+          <t>46,31; 56,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,69; 52,3</t>
+          <t>42,84; 53,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,21; 37,07</t>
+          <t>27,38; 35,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,14; 57,5</t>
+          <t>46,53; 57,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,94; 66,18</t>
+          <t>55,45; 66,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,48; 54,93</t>
+          <t>44,65; 54,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 33,88</t>
+          <t>25,85; 33,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44,54; 52,14</t>
+          <t>44,87; 52,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52,48; 59,95</t>
+          <t>52,21; 60,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44,88; 52,06</t>
+          <t>44,69; 52,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,46; 34,18</t>
+          <t>27,91; 33,43</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,05; 49,52</t>
+          <t>40,8; 49,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,21; 61,15</t>
+          <t>52,85; 61,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,69; 59,28</t>
+          <t>50,91; 59,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 33,14</t>
+          <t>26,56; 34,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,11; 63,45</t>
+          <t>47,91; 63,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,73; 75,33</t>
+          <t>64,36; 75,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,03; 73,57</t>
+          <t>58,69; 73,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38,4; 50,68</t>
+          <t>37,97; 50,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,87; 51,62</t>
+          <t>44,27; 51,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57,55; 64,52</t>
+          <t>57,57; 64,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53,88; 61,87</t>
+          <t>54,37; 61,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 36,27</t>
+          <t>30,99; 38,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,42; 51,47</t>
+          <t>45,52; 51,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,95; 60,01</t>
+          <t>54,12; 60,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,94; 56,11</t>
+          <t>50,05; 55,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,87; 40,3</t>
+          <t>32,97; 38,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,81; 63,93</t>
+          <t>55,96; 63,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,22; 66,51</t>
+          <t>59,33; 66,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,19; 57,11</t>
+          <t>50,07; 56,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,03; 71,05</t>
+          <t>33,82; 39,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,21; 54,58</t>
+          <t>50,02; 54,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57,12; 61,81</t>
+          <t>57,05; 61,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,82; 55,4</t>
+          <t>50,88; 55,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,49; 62,19</t>
+          <t>33,95; 38,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,36; 53,69</t>
+          <t>43,21; 54,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52,23; 60,94</t>
+          <t>52,13; 60,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48,49; 56,72</t>
+          <t>48,7; 56,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33,26; 43,21</t>
+          <t>30,45; 38,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,01; 64,93</t>
+          <t>56,58; 64,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,03; 76,66</t>
+          <t>69,79; 76,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,57; 73,41</t>
+          <t>66,78; 73,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,64; 49,23</t>
+          <t>43,62; 49,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52,64; 59,36</t>
+          <t>53,02; 59,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,08; 69,29</t>
+          <t>63,83; 69,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,46; 64,73</t>
+          <t>59,42; 65,09</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>34,03; 44,99</t>
+          <t>39,37; 44,03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19,2; 28,81</t>
+          <t>18,79; 28,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,56; 43,87</t>
+          <t>30,36; 43,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,75; 37,16</t>
+          <t>26,73; 37,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,14; 36,64</t>
+          <t>15,08; 31,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63,75; 69,06</t>
+          <t>63,75; 68,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70,24; 75,22</t>
+          <t>69,8; 75,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,78; 70,59</t>
+          <t>64,71; 70,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,1; 47,78</t>
+          <t>40,72; 47,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55,8; 60,65</t>
+          <t>55,41; 60,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62,89; 68,35</t>
+          <t>63,07; 68,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,67; 62,93</t>
+          <t>57,49; 62,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,63; 43,64</t>
+          <t>36,05; 42,63</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>42,63; 46,16</t>
+          <t>42,65; 46,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,24; 55,66</t>
+          <t>52,19; 55,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,25; 51,66</t>
+          <t>48,09; 51,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,48; 34,7</t>
+          <t>30,77; 34,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,79; 62,1</t>
+          <t>58,46; 62,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,93; 69,19</t>
+          <t>65,87; 69,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,53; 62,91</t>
+          <t>59,51; 62,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38,74; 53,32</t>
+          <t>38,46; 41,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>51,2; 53,68</t>
+          <t>51,36; 53,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59,71; 61,87</t>
+          <t>59,55; 62,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54,46; 56,82</t>
+          <t>54,43; 56,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>33,74; 43,28</t>
+          <t>35,24; 37,47</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160057</t>
+          <t>173661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>151526</t>
+          <t>165777</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>311583</t>
+          <t>339438</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>182396; 226687</t>
+          <t>179766; 225142</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196732; 239453</t>
+          <t>197373; 240025</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168658; 213035</t>
+          <t>169406; 212571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140431; 180816</t>
+          <t>151771; 196176</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>131496; 165635</t>
+          <t>131124; 166732</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>142194; 179107</t>
+          <t>139793; 178830</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>156429; 194818</t>
+          <t>155175; 194912</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>135309; 170259</t>
+          <t>148859; 186106</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>324745; 378626</t>
+          <t>319893; 381675</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>347918; 404971</t>
+          <t>348278; 406859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>340243; 397856</t>
+          <t>337366; 395235</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>284018; 343020</t>
+          <t>312121; 368297</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146340</t>
+          <t>152153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>115138</t>
+          <t>125194</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>261477</t>
+          <t>277347</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>143069; 182993</t>
+          <t>142632; 180880</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>195382; 239947</t>
+          <t>193926; 238473</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>157263; 197306</t>
+          <t>161595; 200235</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127576; 167613</t>
+          <t>132308; 172855</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>175313; 213819</t>
+          <t>173046; 213407</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>185696; 223689</t>
+          <t>187432; 224541</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>165573; 204473</t>
+          <t>166221; 203280</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>99695; 129634</t>
+          <t>109392; 140450</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>329030; 385211</t>
+          <t>331483; 386007</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>397150; 453735</t>
+          <t>395154; 454191</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>336404; 390186</t>
+          <t>334932; 391419</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>237604; 285335</t>
+          <t>252941; 302953</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135352</t>
+          <t>144604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>209373</t>
+          <t>227051</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>222670; 268598</t>
+          <t>221295; 269306</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>334909; 384891</t>
+          <t>332655; 384914</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264580; 309409</t>
+          <t>265704; 310011</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55457; 221450</t>
+          <t>125242; 162016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80721; 106450</t>
+          <t>80384; 107135</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>165781; 195956</t>
+          <t>167428; 197191</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98064; 122223</t>
+          <t>97502; 121840</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64089; 84586</t>
+          <t>71195; 93836</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>311526; 366582</t>
+          <t>314422; 365845</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>511954; 573947</t>
+          <t>512131; 571097</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>370694; 425675</t>
+          <t>374104; 424893</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98770; 302907</t>
+          <t>204262; 250713</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>383057</t>
+          <t>404811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>491896</t>
+          <t>313809</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>874953</t>
+          <t>718620</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>562503; 637395</t>
+          <t>563646; 632856</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>625322; 695489</t>
+          <t>627270; 699443</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>574088; 645111</t>
+          <t>575353; 643581</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>350482; 417016</t>
+          <t>373189; 437359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>398660; 456651</t>
+          <t>399718; 452660</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>454000; 509879</t>
+          <t>454843; 512026</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>414547; 471667</t>
+          <t>413533; 470321</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>352381; 694981</t>
+          <t>291231; 341080</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>980415; 1065684</t>
+          <t>976697; 1067621</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1100000; 1190245</t>
+          <t>1098517; 1186728</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1003980; 1094351</t>
+          <t>1005173; 1095255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>734480; 1251852</t>
+          <t>676657; 759583</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181404</t>
+          <t>196160</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>361159</t>
+          <t>389180</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>542563</t>
+          <t>585340</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>151986; 188196</t>
+          <t>151470; 189582</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>266682; 311180</t>
+          <t>266178; 309776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>300960; 352077</t>
+          <t>302296; 350213</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>158013; 205252</t>
+          <t>172937; 220287</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>318572; 369317</t>
+          <t>321798; 368236</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>533315; 583779</t>
+          <t>531476; 582062</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>491479; 541963</t>
+          <t>492999; 542442</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>274571; 414189</t>
+          <t>362425; 412697</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>483920; 545736</t>
+          <t>487452; 547185</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>815116; 881465</t>
+          <t>812033; 881805</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>808005; 879650</t>
+          <t>807513; 884518</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>447951; 592251</t>
+          <t>550660; 615898</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>340767</t>
+          <t>371728</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>401266</t>
+          <t>423882</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>57264; 85926</t>
+          <t>56040; 85726</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>84236; 117094</t>
+          <t>81015; 115723</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76807; 106710</t>
+          <t>76764; 107428</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41217; 88121</t>
+          <t>35765; 75343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>796023; 862353</t>
+          <t>796058; 861120</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>779183; 834430</t>
+          <t>774324; 832605</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>700978; 763766</t>
+          <t>700203; 762702</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>312937; 363816</t>
+          <t>343784; 399495</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>863143; 938164</t>
+          <t>857206; 939075</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>865567; 940630</t>
+          <t>867999; 938701</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>789649; 861606</t>
+          <t>787120; 861599</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>367038; 437228</t>
+          <t>389922; 461041</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1066708</t>
+          <t>1123542</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1534507</t>
+          <t>1448136</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2601215</t>
+          <t>2571677</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1394034; 1509515</t>
+          <t>1394719; 1510056</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1787502; 1904759</t>
+          <t>1785733; 1901606</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1633597; 1748961</t>
+          <t>1628083; 1741277</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>860155; 1171427</t>
+          <t>1059302; 1181847</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1986096; 2097837</t>
+          <t>1975005; 2094400</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2340512; 2456362</t>
+          <t>2338421; 2456840</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2102521; 2221717</t>
+          <t>2101577; 2221400</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1386144; 1907649</t>
+          <t>1398242; 1504171</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3404040; 3568526</t>
+          <t>3414452; 3573479</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4163000; 4313943</t>
+          <t>4151654; 4322872</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3767104; 3930077</t>
+          <t>3765311; 3938906</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2346399; 3009835</t>
+          <t>2494416; 2652029</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
